--- a/Table/Excel/Text.xlsx
+++ b/Table/Excel/Text.xlsx
@@ -1,91 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Text" state="visible" r:id="rId4"/>
+    <sheet name="Text" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>DataId</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Ko</t>
-  </si>
-  <si>
-    <t>En</t>
-  </si>
-  <si>
-    <t>ui.talk</t>
-  </si>
-  <si>
-    <t>대화하기</t>
-  </si>
-  <si>
-    <t>Talk</t>
-  </si>
-  <si>
-    <t>ui.move</t>
-  </si>
-  <si>
-    <t>이동하기</t>
-  </si>
-  <si>
-    <t>Move</t>
-  </si>
-  <si>
-    <t>npc.shopkeeper</t>
-  </si>
-  <si>
-    <t>상점 주인</t>
-  </si>
-  <si>
-    <t>Shopkeeper</t>
-  </si>
-  <si>
-    <t>item.rose.name</t>
-  </si>
-  <si>
-    <t>장미</t>
-  </si>
-  <si>
-    <t>Rose</t>
-  </si>
-  <si>
-    <t>item.rose.desc</t>
-  </si>
-  <si>
-    <t>오늘 들어온 붉은 장미.</t>
-  </si>
-  <si>
-    <t>A red rose that arrived today.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -104,39 +47,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="TextTable" displayName="TextTable" ref="A1:D6" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:D6">
-    <filterColumn colId="0" hiddenButton="0"/>
-    <filterColumn colId="1" hiddenButton="0"/>
-    <filterColumn colId="2" hiddenButton="0"/>
-    <filterColumn colId="3" hiddenButton="0"/>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TextTable" displayName="TextTable" ref="A1:D19" headerRowCount="1">
+  <autoFilter ref="A1:D19"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="DataId" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Key" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Ko" totalsRowFunction="none"/>
-    <tableColumn id="4" name="En" totalsRowFunction="none"/>
+    <tableColumn id="1" name="DataId"/>
+    <tableColumn id="2" name="Key"/>
+    <tableColumn id="3" name="Ko"/>
+    <tableColumn id="4" name="En"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -215,7 +212,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,7 +246,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -285,16 +280,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -416,149 +415,412 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="4" width="36" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>En</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ui.talk</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>대화하기</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ui.move</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>이동하기</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>npc.shopkeeper</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>상점 주인</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shopkeeper</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>item.rose.name</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>장미</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>item.rose.desc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>오늘 들어온 붉은 장미.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A red rose that arrived today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ui.notebook.tab.cover</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>표지</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ui.notebook.tab.quests</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>의뢰</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ui.notebook.tab.residents</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>주민</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Residents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ui.notebook.tab.alibis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>알리바이</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Alibis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ui.notebook.tab.questions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>의문점</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ui.notebook.tab.documents</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>서류</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ui.notebook.case</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>사건 {0}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Case {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>107</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ui.notebook.progress</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>진행도 {0}%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Progress {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>108</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ui.notebook.empty</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>아직 적힌 것이 없다.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nothing written yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>109</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ui.notebook.close</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>닫기</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ui.toast.note</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>수첩에 기록됨</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Noted in notebook</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ui.toast.quest</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>새 의뢰: {0}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New request: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ui.toast.questdone</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>의뢰 완료: {0}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Request done: {0}</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Table/Excel/Text.xlsx
+++ b/Table/Excel/Text.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TextTable" displayName="TextTable" ref="A1:D19" headerRowCount="1">
-  <autoFilter ref="A1:D19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TextTable" displayName="TextTable" ref="A1:D39" headerRowCount="1">
+  <autoFilter ref="A1:D39"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key"/>
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -814,6 +814,406 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>Request done: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ui.title.continue</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>이어하기</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ui.title.newgame</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>새로하기</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New Game</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ui.title.settings</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>116</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ui.title.newgame.confirm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>새로 시작하면 지금까지의 기록 위에 덮어씁니다. 시작할까요?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Starting over will overwrite your record. Start?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>117</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ui.pause.header</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>잠시 멈춤</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ui.pause.resume</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>계속하기</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ui.pause.settings</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ui.pause.title</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>타이틀로</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>To Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ui.pause.title.confirm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>마지막 저장 이후의 진행은 사라집니다. 타이틀로 갈까요?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Progress since your last save will be lost. Go to title?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ui.settings.header</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ui.settings.master</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>전체 음량</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ui.settings.bgm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>배경음</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ui.settings.sfx</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>효과음</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ui.settings.language</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>언어</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ui.language.name</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한국어</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ui.confirm.yes</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ui.confirm.no</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>scene.Plaza</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>광장</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>scene.Character</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ui.close</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>닫기</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Close</t>
         </is>
       </c>
     </row>

--- a/Table/Excel/Text.xlsx
+++ b/Table/Excel/Text.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TextTable" displayName="TextTable" ref="A1:D39" headerRowCount="1">
-  <autoFilter ref="A1:D39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TextTable" displayName="TextTable" ref="A1:D41" headerRowCount="1">
+  <autoFilter ref="A1:D41"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1217,6 +1217,46 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ui.inspect</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>조사하기</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Inspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ui.toast.saved</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>수첩에 기록을 정리했다</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Notes saved</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
